--- a/Remaining_Clashes_v2.4.xlsx
+++ b/Remaining_Clashes_v2.4.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clash Detail'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clash Detail'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -55,7 +55,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,6 +111,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -478,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,6 +499,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,1458 +548,3464 @@
           <t>Blocking Courses</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sections Tried</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>106288</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Gerald, Anthony</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per G: period_conflict (851); Sec 2 Per D: period_conflict (440)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>106255</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Gaida, Robert</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>732 Business Law [graduation_required]</t>
         </is>
       </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (732); Sec 2 Per G: period_conflict (744)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>106322</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Jensen, Finn</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>744 Sociology [graduation_required]</t>
         </is>
       </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (851); Sec 2 Per G: period_conflict (744)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>106791</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Guirland, Gavin</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>CPR-AED Training/PE</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Physical Education</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>132 British Literature [graduation_required]</t>
         </is>
       </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per B: period_conflict (132); Sec 2 Per A: period_conflict (830); Sec 3 Per F: period_conflict (430); Sec 4 Per D: period_conflict (955); Sec 5 Per C: period_conflict (530)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>108163</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Mathews, Noah</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Business Law</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>733 AP U.S. History [graduation_required]</t>
         </is>
       </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (131); Sec 2 Per A: period_conflict (733); Sec 3 Per B: period_conflict (443)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>116815</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>DellaVolpe, Louis</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>TV/Film Production II</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>520 Chemistry [graduation_required]</t>
         </is>
       </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (520); Sec 2 Per F: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>116044</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Brudney, Denzin</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (440); Sec 2 Per F: period_conflict (730); Sec 3 Per C: period_conflict (851); Sec 4 Per B: period_conflict (732)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>109471</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Shaikh, Adam</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>International Business Strategies</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>733 AP U.S. History [graduation_required]</t>
         </is>
       </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (139); Sec 2 Per B: period_conflict (733); Sec 3 Per F: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>106869</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Hanabergh, Daniel</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>553 AP Chemistry [graduation_required]</t>
         </is>
       </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (553); Sec 2 Per E: period_conflict (553)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>121012</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>121012</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Robotics</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>110 Composition &amp; Literature [graduation_required]</t>
         </is>
       </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (110); Sec 2 Per C: period_conflict (510)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>110396</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Riccardi, Christian</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>International Business Strategies</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>430 Algebra II/Trig [graduation_required]</t>
         </is>
       </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (130); Sec 2 Per B: period_conflict (520); Sec 3 Per F: period_conflict (430)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>110396</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Riccardi, Christian</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Business Law</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>520 Chemistry [graduation_required]</t>
         </is>
       </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (430); Sec 2 Per A: period_conflict (830); Sec 3 Per B: period_conflict (520)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>108622</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sasso, Daniel</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>131 British Literature H [graduation_required]</t>
         </is>
       </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per G: period_conflict (131); Sec 2 Per D: period_conflict (139)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>108368</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Opiola, Nathaniel</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Sports and Entertainment Marketing</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>330 Spanish III [graduation_required]</t>
         </is>
       </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per D: period_conflict (731); Sec 2 Per E: period_conflict (330); Sec 3 Per A: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>108437</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Basich, Tomislav</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>TV/Film Production &amp; Editing I</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>singleton_collision</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>330 Spanish III [graduation_required]</t>
         </is>
       </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per D: period_conflict (330)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>107632</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Waldow, Aidan</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>International Business Strategies</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>430 Algebra II/Trig [graduation_required]</t>
         </is>
       </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (130); Sec 2 Per B: period_conflict (530); Sec 3 Per F: period_conflict (430)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>107150</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Ferro, Preston</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Studio Art I</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Humanities</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>830 Theology 11 [graduation_required]</t>
         </is>
       </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (530); Sec 2 Per B: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>107177</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Siracuse, David</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>530 Physics [graduation_required]</t>
         </is>
       </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (530); Sec 2 Per E: period_conflict (530)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>106794</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Campbell, Kevin</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>International Business Strategies</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>430 Algebra II/Trig [graduation_required]</t>
         </is>
       </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (530); Sec 2 Per B: period_conflict (131); Sec 3 Per F: period_conflict (430)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>119656</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Pierce, Dylan</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Sports and Entertainment Marketing</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>830 Theology 11 [graduation_required]</t>
         </is>
       </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per D: period_conflict (720); Sec 2 Per E: period_conflict (330); Sec 3 Per A: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>110098</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Arment, Jayden</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Studio Art I</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Humanities</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>830 Theology 11 [graduation_required]</t>
         </is>
       </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (130); Sec 2 Per B: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="3" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>107073</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Russo, Gavin</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Business Law</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>330 Spanish III [graduation_required]</t>
         </is>
       </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (130); Sec 2 Per A: period_conflict (330); Sec 3 Per B: period_conflict (530)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>111356</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Janos, Frank</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>830 Theology 11 [graduation_required]</t>
         </is>
       </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (830); Sec 2 Per E: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="3" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>106253</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>McLaughlin, Colin</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (851); Sec 2 Per G: period_conflict (440)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>106236</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Ambrosio, Anthony</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>752 Economics H [graduation_required]</t>
         </is>
       </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (752); Sec 2 Per G: period_conflict (440)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="3" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>106213</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Silvestri, Lucas</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>752 Economics H [graduation_required]</t>
         </is>
       </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (141); Sec 2 Per G: period_conflict (752)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>106316</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Olivero Gamez, Josue</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>440 Precalculus [graduation_required]</t>
         </is>
       </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (440); Sec 2 Per G: period_conflict (140)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="3" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>112468</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Gil, Nicholas</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>732 Business Law [graduation_required]</t>
         </is>
       </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (732); Sec 2 Per G: period_conflict (140)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>117247</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Ohnegian, Michael</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Physics H</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>751 American Government &amp; Politics [graduation_required]</t>
         </is>
       </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (744); Sec 2 Per G: period_conflict (450); Sec 3 Per A: period_conflict (751)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="3" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>106283</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Skennion, Liam</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>440 Precalculus [graduation_required]</t>
         </is>
       </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (440); Sec 2 Per B: period_conflict (359)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="3" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>106264</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Hanna, Joseph</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>351 AP Spanish [no_alternative]</t>
         </is>
       </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (140); Sec 2 Per B: period_conflict (351)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="3" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>106263</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Velez, Cristian</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>758 Bloomberg Market Concepts [graduation_required]</t>
         </is>
       </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (758); Sec 2 Per B: period_conflict (351)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="3" t="inlineStr"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>106206</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>DiMaulo, William</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>440 Precalculus [graduation_required]</t>
         </is>
       </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (440); Sec 2 Per B: period_conflict (851)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="3" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>106199</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Dos Santos, Antonio</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>758 Bloomberg Market Concepts [graduation_required]</t>
         </is>
       </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (758); Sec 2 Per B: period_conflict (766)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="3" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>106211</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Ruggiero, Richard</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>141 College English Honors [graduation_required]</t>
         </is>
       </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per G: period_conflict (440); Sec 2 Per D: period_conflict (141)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="3" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>106234</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Abromowicz, Gavin</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>758 Bloomberg Market Concepts [graduation_required]</t>
         </is>
       </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (758); Sec 2 Per B: period_conflict (443)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="3" t="inlineStr"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>106336</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Kang, Won</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>149 AP English Literature [graduation_required]</t>
         </is>
       </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (149); Sec 2 Per B: period_conflict (732)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="3" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>106332</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Scialla, Rocco</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>732 Business Law [graduation_required]</t>
         </is>
       </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (440); Sec 2 Per B: period_conflict (732)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="3" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>106333</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Minnich, Andrew</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (743); Sec 2 Per G: period_conflict (851)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="3" t="inlineStr"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>106333</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Minnich, Andrew</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Anatomy/Physiology H</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>741 Psychology [graduation_required]</t>
         </is>
       </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per A: period_conflict (149); Sec 2 Per B: period_conflict (741)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="3" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>106295</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Field, Dylan</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>TV/Film Production II</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>761 AP Psychology [graduation_required]</t>
         </is>
       </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (761); Sec 2 Per F: period_conflict (453)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="3" t="inlineStr"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>106219</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Konecni, Joshua</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>455 AP Calc BC [graduation_required]</t>
         </is>
       </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (763); Sec 2 Per G: period_conflict (149)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="3" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>115730</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Skirmants, Henrijs</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Physics H</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>443 AP Precalculus [graduation_required]</t>
         </is>
       </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (761); Sec 2 Per G: period_conflict (149); Sec 3 Per A: period_conflict (443)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="3" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>106170</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Puleo, Tyler</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Studio Art I</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Humanities</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>440 Precalculus [graduation_required]</t>
         </is>
       </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (440); Sec 2 Per B: period_conflict (851)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="3" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>110478</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Weintraub, Jason</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>763 AP U.S. Government &amp; Politics [graduation_required]</t>
         </is>
       </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (743); Sec 2 Per G: period_conflict (763)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="3" t="inlineStr"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>106290</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Potenza, Nicolas</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>585 Robotics Design [no_alternative]</t>
         </is>
       </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (585); Sec 2 Per G: period_conflict (450)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="3" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>106196</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Hauck, Thomas</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>763 AP U.S. Government &amp; Politics [graduation_required]</t>
         </is>
       </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (766); Sec 2 Per G: period_conflict (763)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="3" t="inlineStr"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>106241</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Kosoff, Luke</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>765 AP Macroeconomics [graduation_required]</t>
         </is>
       </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (763); Sec 2 Per G: period_conflict (765)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="3" t="inlineStr"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>107648</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Khym, Logan</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Business Law</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>331 Spanish III H [graduation_required]</t>
         </is>
       </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (530); Sec 2 Per A: period_conflict (331); Sec 3 Per B: period_conflict (443)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="3" t="inlineStr"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>106277</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Schulz, Christopher</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (752); Sec 2 Per G: period_conflict (851)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="3" t="inlineStr"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>106222</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Esquivel, Alejandro</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (851); Sec 2 Per G: period_conflict (744)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="3" t="inlineStr"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>106233</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>McLaughlin, Joseph</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>141 College English Honors [graduation_required]</t>
         </is>
       </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (141); Sec 2 Per G: period_conflict (752)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="3" t="inlineStr"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>108756</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Pacheco Guerrero, Adam</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>752 Economics H [graduation_required]</t>
         </is>
       </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (141); Sec 2 Per G: period_conflict (752)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="3" t="inlineStr"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>106249</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Larrondo, Gavin</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>595 Engineering Design [no_alternative]</t>
         </is>
       </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (763); Sec 2 Per G: period_conflict (595)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="3" t="inlineStr"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>106249</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Larrondo, Gavin</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>141 College English Honors [graduation_required]</t>
         </is>
       </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (141); Sec 2 Per E: period_conflict (141)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="3" t="inlineStr"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>121384</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Ryzy, Martin</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>CPR-AED Training/PE</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Physical Education</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>331 Spanish III H [graduation_required]</t>
         </is>
       </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per B: period_conflict (131); Sec 2 Per A: period_conflict (440); Sec 3 Per F: period_conflict (331); Sec 4 Per D: period_conflict (720); Sec 5 Per C: period_conflict (830)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="3" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>116201</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Best, Charles</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>International Business Strategies</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>631 CPR-AED Training/PE [flexible]</t>
         </is>
       </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per C: period_conflict (830); Sec 2 Per B: period_conflict (631); Sec 3 Per F: period_conflict (131)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="3" t="inlineStr"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>108666</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Foye, John</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>CPR-AED Training/PE</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Physical Education</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>131 British Literature H [graduation_required]</t>
         </is>
       </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per B: period_conflict (131); Sec 2 Per A: period_conflict (731); Sec 3 Per F: period_conflict (830); Sec 4 Per D: period_conflict (440); Sec 5 Per C: period_conflict (339)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="3" t="inlineStr"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>112051</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Lane, Dashiell</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>440 Precalculus [graduation_required]</t>
         </is>
       </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (141); Sec 2 Per G: period_conflict (440)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="3" t="inlineStr"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>106337</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Pocsi, Joseph</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>440 Precalculus [graduation_required]</t>
         </is>
       </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per G: period_conflict (440); Sec 2 Per D: period_conflict (851)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="3" t="inlineStr"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>106235</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Mena, Giancarlo</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (440); Sec 2 Per G: period_conflict (851)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="3" t="inlineStr"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>106218</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Zervoudis, Stylianos</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>595 Engineering Design [no_alternative]</t>
         </is>
       </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (851); Sec 2 Per G: period_conflict (595)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="3" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>106239</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>DeFilippo, Daniel</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (851); Sec 2 Per G: period_conflict (752)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="3" t="inlineStr"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>106239</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>DeFilippo, Daniel</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>141 College English Honors [graduation_required]</t>
         </is>
       </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per E: period_conflict (141); Sec 2 Per E: period_conflict (141)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="3" t="inlineStr"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>106323</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Gebert, Evan</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (851); Sec 2 Per G: period_conflict (752)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="3" t="inlineStr"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>107254</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Butler, Jayden</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (851); Sec 2 Per G: period_conflict (140)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="3" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>113957</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Svec, Dylan</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>201 Introduction to Guitar [no_alternative]</t>
         </is>
       </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (201); Sec 2 Per G: period_conflict (440)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="3" t="inlineStr"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>106169</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Infantolino, Anthony</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>851 Spirituality of Vocation [graduation_required]</t>
         </is>
       </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (752); Sec 2 Per G: period_conflict (851)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="3" t="inlineStr"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>111850</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Dukes, Steven</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>140 World Literature [graduation_required]</t>
         </is>
       </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Sec 1 Per F: period_conflict (440); Sec 2 Per G: period_conflict (140)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2000,7 +4016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2008,26 +4024,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Remaining Clashes — v2.4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Total clashes: 69</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Students affected: 1</t>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Students affected: 65</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>By Department</t>
         </is>
@@ -2046,75 +4062,86 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Science</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>69</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Physical Education</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Humanities</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>By Grade</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Grade 9</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Grade 11</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Grade 12</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>By Root Cause</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Root Cause</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
@@ -2124,51 +4151,110 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Grade 9</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>69</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Grade 11</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>By Priority Band</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Priority Band</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Grade 12</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>flexible</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
+          <t>By Root Cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>singleton_collision</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>By Priority Band</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Priority Band</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>limited_choice</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B28" s="2" t="n">
         <v>11</v>
       </c>
     </row>
